--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105347_W3.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105347_W3.xlsx
@@ -570,58 +570,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9949</v>
+        <v>2.9317</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5803</v>
+        <v>3.5462</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5854</v>
+        <v>-0.6145</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4817</v>
+        <v>2.4114</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9757</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>1.506</v>
+        <v>1.4754</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2617</v>
+        <v>3.2789</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4894</v>
+        <v>1.5004</v>
       </c>
       <c r="L2" t="n">
-        <v>1.7724</v>
+        <v>1.7784</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.78</v>
+        <v>-0.8675</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.5644</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2664</v>
+        <v>-0.3031</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2824</v>
+        <v>0.2908</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3185</v>
+        <v>0.2673</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0361</v>
+        <v>0.0235</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -653,67 +653,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8631</v>
+        <v>2.9047</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9107</v>
+        <v>3.5948</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0476</v>
+        <v>-0.6901</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4943</v>
+        <v>-0.6034</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5586</v>
+        <v>0.993</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9357</v>
+        <v>-1.5964</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6763</v>
+        <v>1.461</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9039</v>
+        <v>1.3869</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7724</v>
+        <v>0.0741</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.182</v>
+        <v>-2.0644</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3454</v>
+        <v>-0.3939</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8366</v>
+        <v>-1.6705</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6923</v>
+        <v>1.377</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6923</v>
+        <v>1.377</v>
       </c>
       <c r="S3" t="n">
-        <v>0.292</v>
+        <v>0.3573</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2344</v>
+        <v>0.3599</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0576</v>
+        <v>-0.0026</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.6155</v>
+        <v>1.7739</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.7739</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.6155</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8569</v>
+        <v>2.8742</v>
       </c>
       <c r="E4" t="n">
-        <v>3.504</v>
+        <v>4.9687</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6471</v>
+        <v>-2.0945</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6571</v>
+        <v>3.4971</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8769</v>
+        <v>2.6011</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.534</v>
+        <v>0.896</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2951</v>
+        <v>4.7822</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2213</v>
+        <v>3.0038</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0738</v>
+        <v>1.7784</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9522</v>
+        <v>-1.2851</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3444</v>
+        <v>-0.4027</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6078</v>
+        <v>-0.8824</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3845</v>
+        <v>0.6885</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3845</v>
+        <v>0.6885</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3678</v>
+        <v>0.3116</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4472</v>
+        <v>0.1865</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0794</v>
+        <v>0.1252</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7617</v>
+        <v>-1.623</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7617</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.623</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,64 +819,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4066</v>
+        <v>1.3437</v>
       </c>
       <c r="E5" t="n">
-        <v>2.069</v>
+        <v>2.0402</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6624</v>
+        <v>-0.6965</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1077</v>
+        <v>-0.1622</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1077</v>
+        <v>2.0608</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.2155</v>
+        <v>-2.223</v>
       </c>
       <c r="J5" t="n">
-        <v>1.105</v>
+        <v>1.1524</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9463</v>
+        <v>1.9608</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.8413</v>
+        <v>-0.8084</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2128</v>
+        <v>-1.3146</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1614</v>
+        <v>0.1</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3742</v>
+        <v>-1.4146</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7452</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6563</v>
+        <v>0.5763</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1591</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0701</v>
+        <v>0.99</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8145</v>
+        <v>1.7624</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.7724</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.8898</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0434</v>
+        <v>1.0042</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.057</v>
+        <v>-0.1144</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2924</v>
+        <v>1.3017</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2186</v>
+        <v>1.2276</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0738</v>
+        <v>0.0741</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.306</v>
+        <v>-0.4119</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1751</v>
+        <v>-0.2234</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1309</v>
+        <v>-0.1885</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.923</v>
+        <v>-0.918</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3989</v>
+        <v>1.4083</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0757</v>
+        <v>0.9949</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3232</v>
+        <v>0.4134</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3923</v>
+        <v>-0.3901</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8309</v>
+        <v>0.8427</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2232</v>
+        <v>-1.2329</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7426</v>
+        <v>0.721</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.6644</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.0566</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3244</v>
+        <v>0.2881</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0759</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2258</v>
+        <v>0.2122</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.7322</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1015</v>
+        <v>0.1023</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6277</v>
+        <v>0.6299</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4049</v>
+        <v>-0.4441</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0029</v>
+        <v>-0.0264</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.402</v>
+        <v>-0.4176</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1875</v>
+        <v>0.2034</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0625</v>
+        <v>-0.0678</v>
       </c>
       <c r="U7" t="n">
-        <v>0.25</v>
+        <v>0.2712</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1068,67 +1068,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4795</v>
+        <v>0.5326</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2793</v>
+        <v>1.39</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7998</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.416</v>
+        <v>-4.3592</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3473</v>
+        <v>0.4203</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.7633</v>
+        <v>-4.7795</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6261</v>
+        <v>-1.4035</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0196</v>
+        <v>0.1763</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.6457</v>
+        <v>-1.5798</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.7898</v>
+        <v>-2.9556</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3277</v>
+        <v>0.244</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.1175</v>
+        <v>-3.1997</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0768</v>
+        <v>2.0655</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5107</v>
+        <v>1.4982</v>
       </c>
       <c r="T8" t="n">
-        <v>1.059</v>
+        <v>0.9245</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4517</v>
+        <v>0.5737</v>
       </c>
       <c r="V8" t="n">
-        <v>2.6925</v>
+        <v>2.705</v>
       </c>
       <c r="W8" t="n">
-        <v>3.2309</v>
+        <v>3.2461</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5385</v>
+        <v>-0.541</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1151,64 +1151,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4165</v>
+        <v>0.4247</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5392</v>
+        <v>1.1191</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1227</v>
+        <v>-0.6944</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.8592</v>
+        <v>-3.0301</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4094</v>
+        <v>-1.4975</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.4499</v>
+        <v>-1.5326</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1924</v>
+        <v>-0.3511</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2293</v>
+        <v>-1.0684</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0369</v>
+        <v>0.7173</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.6668</v>
+        <v>-2.679</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.18</v>
+        <v>-0.4292</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.4868</v>
+        <v>-2.2498</v>
       </c>
       <c r="P9" t="n">
-        <v>1.846</v>
+        <v>1.6065</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2308</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0768</v>
+        <v>1.6065</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2835</v>
+        <v>0.6155</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8162</v>
+        <v>0.2373</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4674</v>
+        <v>0.3781</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1462</v>
+        <v>1.2329</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1462</v>
+        <v>1.2329</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1234,64 +1234,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3359</v>
+        <v>0.3937</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9948</v>
+        <v>1.5751</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6589</v>
+        <v>-1.1815</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0987</v>
+        <v>-3.836</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5642</v>
+        <v>-0.3029</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5345</v>
+        <v>-3.5331</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5723</v>
+        <v>0.0017</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2159</v>
+        <v>-0.0354</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.0371</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5264</v>
+        <v>-3.8376</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3483</v>
+        <v>-0.2675</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.1781</v>
+        <v>-3.5702</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6153</v>
+        <v>1.836</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.2295</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6153</v>
+        <v>2.0655</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5961</v>
+        <v>2.2428</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3439</v>
+        <v>1.6521</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2522</v>
+        <v>0.5907</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2232</v>
+        <v>0.1509</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2232</v>
+        <v>0.1509</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1317,67 +1317,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1452</v>
+        <v>-0.1117</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5526</v>
+        <v>0.6038</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6978</v>
+        <v>-0.7155</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2848</v>
+        <v>1.2985</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8139</v>
+        <v>1.8508</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5291</v>
+        <v>-0.5523</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5561</v>
+        <v>1.6456</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4822</v>
+        <v>1.5715</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0738</v>
+        <v>0.0741</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2713</v>
+        <v>-0.3471</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3316</v>
+        <v>0.2793</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6029</v>
+        <v>-0.6264</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6923</v>
+        <v>-0.6885</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4855</v>
+        <v>0.5111</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1503</v>
+        <v>0.1056</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3352</v>
+        <v>0.4055</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2232</v>
+        <v>-1.2329</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2232</v>
+        <v>-1.2329</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.2663</v>
+        <v>-13.1126</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.6374</v>
+        <v>-10.4328</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6289</v>
+        <v>-2.6798</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.418100000000001</v>
+        <v>-8.261799999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6382</v>
+        <v>0.6038</v>
       </c>
       <c r="I12" t="n">
-        <v>-9.0564</v>
+        <v>-8.865600000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.661</v>
+        <v>-5.3533</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4788</v>
+        <v>0.5215</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.1398</v>
+        <v>-5.8748</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.7571</v>
+        <v>-2.9085</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1594</v>
+        <v>0.0824</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.9166</v>
+        <v>-2.9908</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.1536</v>
+        <v>-4.1309</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.9996</v>
+        <v>-5.9669</v>
       </c>
       <c r="R12" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7054</v>
+        <v>1.6834</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2693</v>
+        <v>1.1266</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4361</v>
+        <v>0.5568</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.4</v>
+        <v>-2.4033</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2461</v>
+        <v>-0.2393</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.154</v>
+        <v>-2.164</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2453999999999983</v>
+        <v>-0.1079999999999988</v>
       </c>
       <c r="E13" t="n">
-        <v>10.2738</v>
+        <v>10.8319</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.5193</v>
+        <v>-10.94</v>
       </c>
       <c r="G13" t="n">
-        <v>-11.9852</v>
+        <v>-11.8678</v>
       </c>
       <c r="H13" t="n">
-        <v>8.486700000000001</v>
+        <v>8.7455</v>
       </c>
       <c r="I13" t="n">
-        <v>-20.4722</v>
+        <v>-20.6133</v>
       </c>
       <c r="J13" t="n">
-        <v>5.864100000000002</v>
+        <v>7.247800000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>9.416400000000001</v>
+        <v>10.3473</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.5524</v>
+        <v>-3.0996</v>
       </c>
       <c r="M13" t="n">
-        <v>-17.8493</v>
+        <v>-19.1154</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9296</v>
+        <v>-1.6018</v>
       </c>
       <c r="O13" t="n">
-        <v>-16.9198</v>
+        <v>-17.5136</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1539</v>
+        <v>1.147600000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.384</v>
+        <v>-10.3274</v>
       </c>
       <c r="R13" t="n">
-        <v>11.5378</v>
+        <v>11.475</v>
       </c>
       <c r="S13" t="n">
-        <v>9.855</v>
+        <v>9.857800000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>7.308299999999999</v>
+        <v>6.3632</v>
       </c>
       <c r="U13" t="n">
-        <v>2.5468</v>
+        <v>3.4946</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7311000000000001</v>
+        <v>0.7544</v>
       </c>
       <c r="W13" t="n">
-        <v>7.485300000000001</v>
+        <v>7.5482</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.7544</v>
+        <v>-6.793800000000001</v>
       </c>
       <c r="Y13" t="inlineStr"/>
     </row>
@@ -1562,67 +1562,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4942</v>
+        <v>5.4873</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0324</v>
+        <v>6.0598</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5382</v>
+        <v>-0.5725</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2014</v>
+        <v>5.1784</v>
       </c>
       <c r="H14" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0318</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1077</v>
+        <v>5.1466</v>
       </c>
       <c r="J14" t="n">
-        <v>6.119</v>
+        <v>6.178</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6093</v>
+        <v>0.6138</v>
       </c>
       <c r="L14" t="n">
-        <v>5.5097</v>
+        <v>5.5642</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9175</v>
+        <v>-0.9997</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.582</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.402</v>
+        <v>-0.4176</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.846</v>
+        <v>-1.836</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S14" t="n">
-        <v>0.131</v>
+        <v>0.1317</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0793</v>
+        <v>-0.1382</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2103</v>
+        <v>0.2699</v>
       </c>
       <c r="V14" t="n">
-        <v>2.0078</v>
+        <v>2.0132</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3002</v>
+        <v>2.3149</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2924</v>
+        <v>-0.3017</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1645,64 +1645,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7353</v>
+        <v>2.7332</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6428</v>
+        <v>1.6795</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0925</v>
+        <v>1.0537</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8764</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0643</v>
+        <v>-1.0566</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9406</v>
+        <v>1.9401</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7873</v>
+        <v>0.9395</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8823</v>
+        <v>-0.7715</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6695</v>
+        <v>1.711</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0891</v>
+        <v>-0.056</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.182</v>
+        <v>-0.2851</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2711</v>
+        <v>0.2291</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.518</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3676</v>
+        <v>-0.4929</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1504</v>
+        <v>-0.0378</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2232</v>
+        <v>1.2329</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2232</v>
+        <v>1.2329</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1728,67 +1728,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7306</v>
+        <v>2.6863</v>
       </c>
       <c r="E16" t="n">
-        <v>1.171</v>
+        <v>1.1946</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5596</v>
+        <v>1.4917</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1161</v>
+        <v>2.0847</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.6393</v>
+        <v>-2.6511</v>
       </c>
       <c r="I16" t="n">
-        <v>4.7553</v>
+        <v>4.7358</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8319</v>
+        <v>1.9848</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.61</v>
+        <v>-1.5046</v>
       </c>
       <c r="L16" t="n">
-        <v>3.4419</v>
+        <v>3.4894</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2842</v>
+        <v>0.1</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0292</v>
+        <v>-1.1464</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3134</v>
+        <v>1.2464</v>
       </c>
       <c r="P16" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0768</v>
+        <v>2.0655</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0853</v>
+        <v>-1.0836</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4301</v>
+        <v>-0.5607</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6552</v>
+        <v>-0.5229</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4221</v>
+        <v>1.3937</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8237</v>
+        <v>1.8716</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4016</v>
+        <v>-0.4778</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3059</v>
+        <v>3.3005</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2755</v>
+        <v>1.1989</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0304</v>
+        <v>2.1016</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8967</v>
+        <v>4.0649</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1374</v>
+        <v>2.1924</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7593</v>
+        <v>1.8725</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5908</v>
+        <v>-0.7644</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8619</v>
+        <v>-0.9936</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2711</v>
+        <v>0.2291</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0768</v>
+        <v>2.0655</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.822</v>
+        <v>-0.8345</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3039</v>
+        <v>-0.4394</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5181</v>
+        <v>-0.3951</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8309</v>
+        <v>-0.8427</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3694</v>
+        <v>-1.3838</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,67 +1894,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2711</v>
+        <v>1.2003</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6969</v>
+        <v>0.6718</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5742</v>
+        <v>0.5285</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4089</v>
+        <v>1.316</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0069</v>
+        <v>-0.0617</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4158</v>
+        <v>1.3777</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1139</v>
+        <v>1.1191</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3385</v>
+        <v>0.341</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7754</v>
+        <v>0.7781</v>
       </c>
       <c r="M18" t="n">
-        <v>0.295</v>
+        <v>0.1969</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3454</v>
+        <v>-0.4027</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6403</v>
+        <v>0.5996</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="S18" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0352</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1862</v>
+        <v>-0.2178</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1946</v>
+        <v>0.253</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1977,22 +1977,22 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1683</v>
+        <v>0.1617</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1683</v>
+        <v>0.1617</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1683</v>
+        <v>0.1617</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1683</v>
+        <v>0.1617</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2004,13 +2004,13 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1683</v>
+        <v>0.1617</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1683</v>
+        <v>0.1617</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0123</v>
+        <v>-0.0181</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6248</v>
+        <v>-0.6188</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6371</v>
+        <v>0.6007</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3195</v>
+        <v>2.2791</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9544</v>
+        <v>1.8985</v>
       </c>
       <c r="I20" t="n">
-        <v>0.365</v>
+        <v>0.3806</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9927</v>
+        <v>2.0439</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1325</v>
+        <v>2.1484</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1398</v>
+        <v>-0.1045</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3267</v>
+        <v>0.2352</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1781</v>
+        <v>-0.2498</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5048</v>
+        <v>0.4851</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R20" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7764</v>
+        <v>-0.7693</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.31</v>
+        <v>-0.3677</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4664</v>
+        <v>-0.4016</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,64 +2143,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2371</v>
+        <v>-0.2122</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0515</v>
+        <v>0.0188</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1856</v>
+        <v>-0.2311</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3073</v>
+        <v>0.2912</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6939</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0012</v>
+        <v>0.9903</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0624</v>
+        <v>1.1821</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5006</v>
+        <v>0.5826</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5618</v>
+        <v>0.5995</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7552</v>
+        <v>-0.8909</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1945</v>
+        <v>-1.2817</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4394</v>
+        <v>0.3908</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4615</v>
+        <v>-0.459</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="R21" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6214</v>
+        <v>-0.5855</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2679</v>
+        <v>-0.3273</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3535</v>
+        <v>-0.2582</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2226,67 +2226,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2893</v>
+        <v>-0.2812</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7132</v>
+        <v>1.7861</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0025</v>
+        <v>-2.0673</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.061</v>
+        <v>-1.0231</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.7717</v>
+        <v>-2.761</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7107</v>
+        <v>1.738</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9413</v>
+        <v>1.1291</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0685</v>
+        <v>-0.959</v>
       </c>
       <c r="L22" t="n">
-        <v>2.0098</v>
+        <v>2.0881</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0024</v>
+        <v>-2.1522</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7032</v>
+        <v>-1.802</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2991</v>
+        <v>-0.3502</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="R22" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4591</v>
+        <v>-0.4877</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.1956</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3847</v>
+        <v>-0.2921</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="W22" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5385</v>
+        <v>-0.541</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2309,67 +2309,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7018</v>
+        <v>-1.6727</v>
       </c>
       <c r="E23" t="n">
-        <v>2.8071</v>
+        <v>2.8868</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.509</v>
+        <v>-4.5595</v>
       </c>
       <c r="G23" t="n">
-        <v>1.7849</v>
+        <v>1.8241</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1553</v>
+        <v>-0.1799</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9402</v>
+        <v>2.004</v>
       </c>
       <c r="J23" t="n">
-        <v>2.8766</v>
+        <v>3.0383</v>
       </c>
       <c r="K23" t="n">
-        <v>1.3758</v>
+        <v>1.4252</v>
       </c>
       <c r="L23" t="n">
-        <v>1.5008</v>
+        <v>1.6132</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0917</v>
+        <v>-1.2142</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5311</v>
+        <v>-1.6051</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4394</v>
+        <v>0.3908</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.923</v>
+        <v>-0.918</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9482</v>
+        <v>-0.9558</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0073</v>
+        <v>-0.0861</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9556</v>
+        <v>-0.8697</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.6155</v>
+        <v>-1.623</v>
       </c>
       <c r="W23" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.6925</v>
+        <v>-2.705</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,58 +2392,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5557</v>
+        <v>-3.4907</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8772</v>
+        <v>-3.7728</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3215</v>
+        <v>0.2821</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.0173</v>
+        <v>-2.9326</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.2716</v>
+        <v>-3.202</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2543</v>
+        <v>0.2694</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.2681</v>
+        <v>-2.0946</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.756</v>
+        <v>-2.62</v>
       </c>
       <c r="L24" t="n">
-        <v>0.488</v>
+        <v>0.5254</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7493</v>
+        <v>-0.838</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.582</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2337</v>
+        <v>-0.2559</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3845</v>
+        <v>1.377</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7692</v>
+        <v>-0.7876</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4554</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3137</v>
+        <v>-0.2569</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0307</v>
+        <v>-4.098</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8144</v>
+        <v>-0.8375</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2164</v>
+        <v>-3.2606</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.4249</v>
+        <v>-1.4959</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.2075</v>
+        <v>-1.2635</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2173</v>
+        <v>-0.2324</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5044</v>
+        <v>-0.4697</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1523</v>
+        <v>0.1535</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6567</v>
+        <v>-0.6232</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9205</v>
+        <v>-1.0261</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.3599</v>
+        <v>-1.4169</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4394</v>
+        <v>0.3908</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2212</v>
+        <v>-0.2086</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0793</v>
+        <v>-0.1382</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1419</v>
+        <v>-0.0704</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.154</v>
+        <v>-2.164</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.154</v>
+        <v>-2.164</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2558,67 +2558,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>4.019299999999997</v>
+        <v>3.889600000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>10.5192</v>
+        <v>10.9399</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.500100000000001</v>
+        <v>-7.0504</v>
       </c>
       <c r="G26" t="n">
-        <v>11.9855</v>
+        <v>11.8677</v>
       </c>
       <c r="H26" t="n">
-        <v>-8.486899999999999</v>
+        <v>-8.745699999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>20.4722</v>
+        <v>20.61340000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>17.8493</v>
+        <v>19.1154</v>
       </c>
       <c r="K26" t="n">
-        <v>0.9295999999999999</v>
+        <v>1.6018</v>
       </c>
       <c r="L26" t="n">
-        <v>16.9197</v>
+        <v>17.5137</v>
       </c>
       <c r="M26" t="n">
-        <v>-5.8641</v>
+        <v>-7.2477</v>
       </c>
       <c r="N26" t="n">
-        <v>-9.416499999999997</v>
+        <v>-10.3473</v>
       </c>
       <c r="O26" t="n">
-        <v>3.5524</v>
+        <v>3.0997</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.1537</v>
+        <v>-1.1475</v>
       </c>
       <c r="Q26" t="n">
-        <v>-11.5378</v>
+        <v>-11.475</v>
       </c>
       <c r="R26" t="n">
-        <v>10.384</v>
+        <v>10.3275</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.081399999999999</v>
+        <v>-6.0764</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.5468</v>
+        <v>-3.4946</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.5346</v>
+        <v>-2.5818</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.7309999999999999</v>
+        <v>-0.7543</v>
       </c>
       <c r="W26" t="n">
-        <v>6.7544</v>
+        <v>6.793800000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.4854</v>
+        <v>-7.5482</v>
       </c>
       <c r="Y26" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105347_W3.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105347_W3.xlsx
@@ -570,58 +570,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9317</v>
+        <v>2.9388</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5462</v>
+        <v>3.4616</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6145</v>
+        <v>-0.5228</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4114</v>
+        <v>2.4026</v>
       </c>
       <c r="H2" t="n">
         <v>0.9360000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4754</v>
+        <v>1.4665</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2789</v>
+        <v>3.218</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5004</v>
+        <v>1.461</v>
       </c>
       <c r="L2" t="n">
-        <v>1.7784</v>
+        <v>1.7569</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8675</v>
+        <v>-0.8154</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5644</v>
+        <v>-0.525</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3031</v>
+        <v>-0.2904</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2908</v>
+        <v>0.3022</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2673</v>
+        <v>0.2436</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0235</v>
+        <v>0.0586</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -653,67 +653,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9047</v>
+        <v>2.8524</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5948</v>
+        <v>4.8037</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6901</v>
+        <v>-1.9514</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6034</v>
+        <v>3.4165</v>
       </c>
       <c r="H3" t="n">
-        <v>0.993</v>
+        <v>2.5205</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.5964</v>
+        <v>0.896</v>
       </c>
       <c r="J3" t="n">
-        <v>1.461</v>
+        <v>4.6409</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3869</v>
+        <v>2.884</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0741</v>
+        <v>1.7569</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0644</v>
+        <v>-1.2244</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3939</v>
+        <v>-0.3635</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6705</v>
+        <v>-0.8609</v>
       </c>
       <c r="P3" t="n">
-        <v>1.377</v>
+        <v>0.7019</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.377</v>
+        <v>0.7019</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3573</v>
+        <v>0.3301</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3599</v>
+        <v>0.1628</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0026</v>
+        <v>0.1673</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7739</v>
+        <v>-1.5962</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7739</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.5962</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8742</v>
+        <v>2.8405</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9687</v>
+        <v>3.3896</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0945</v>
+        <v>-0.5491</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4971</v>
+        <v>-0.6531</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6011</v>
+        <v>0.9096</v>
       </c>
       <c r="I4" t="n">
-        <v>0.896</v>
+        <v>-1.5627</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7822</v>
+        <v>1.3418</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0038</v>
+        <v>1.2686</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7784</v>
+        <v>0.0732</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2851</v>
+        <v>-1.9949</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4027</v>
+        <v>-0.359</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8824</v>
+        <v>-1.6359</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6885</v>
+        <v>1.4038</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6885</v>
+        <v>1.4038</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3116</v>
+        <v>0.3593</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1865</v>
+        <v>0.3173</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1252</v>
+        <v>0.042</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.623</v>
+        <v>1.7305</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.7305</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.623</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,64 +819,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3437</v>
+        <v>1.3558</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0402</v>
+        <v>1.9427</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6965</v>
+        <v>-0.5869</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1622</v>
+        <v>-0.1567</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0608</v>
+        <v>2.0394</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.223</v>
+        <v>-2.1962</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1524</v>
+        <v>1.1016</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9608</v>
+        <v>1.9093</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.8084</v>
+        <v>-0.8077</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3146</v>
+        <v>-1.2584</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1</v>
+        <v>0.1301</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4146</v>
+        <v>-1.3885</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="R5" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5763</v>
+        <v>0.543</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1591</v>
+        <v>0.2035</v>
       </c>
       <c r="V5" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="W5" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.99</v>
+        <v>1.0159</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7624</v>
+        <v>1.636</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7724</v>
+        <v>-0.6201</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8898</v>
+        <v>0.9038</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0042</v>
+        <v>1.0024</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1144</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3017</v>
+        <v>1.2686</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2276</v>
+        <v>1.1954</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0741</v>
+        <v>0.0732</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4119</v>
+        <v>-0.3648</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2234</v>
+        <v>-0.193</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1885</v>
+        <v>-0.1718</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.918</v>
+        <v>-0.9359</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="R6" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4083</v>
+        <v>1.4457</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9949</v>
+        <v>0.9705</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4134</v>
+        <v>0.4751</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3901</v>
+        <v>-0.3978</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8427</v>
+        <v>0.8007</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.721</v>
+        <v>0.7507</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6644</v>
+        <v>0.6494</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0566</v>
+        <v>0.1013</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2881</v>
+        <v>0.2994</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0759</v>
+        <v>0.0861</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2122</v>
+        <v>0.2133</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7322</v>
+        <v>0.7219</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1023</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6299</v>
+        <v>0.6222</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4441</v>
+        <v>-0.4224</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0264</v>
+        <v>-0.0135</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4176</v>
+        <v>-0.409</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2034</v>
+        <v>0.2173</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0678</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2712</v>
+        <v>0.2897</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1068,67 +1068,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5326</v>
+        <v>0.5379</v>
       </c>
       <c r="E8" t="n">
-        <v>1.39</v>
+        <v>1.1668</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.629</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.3592</v>
+        <v>-4.3493</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4203</v>
+        <v>0.3725</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.7795</v>
+        <v>-4.7218</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4035</v>
+        <v>-1.489</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1763</v>
+        <v>0.0898</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5798</v>
+        <v>-1.5788</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.9556</v>
+        <v>-2.8603</v>
       </c>
       <c r="N8" t="n">
-        <v>0.244</v>
+        <v>0.2827</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.1997</v>
+        <v>-3.143</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4982</v>
+        <v>1.525</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9245</v>
+        <v>0.8673</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5737</v>
+        <v>0.6576</v>
       </c>
       <c r="V8" t="n">
-        <v>2.705</v>
+        <v>2.6603</v>
       </c>
       <c r="W8" t="n">
-        <v>3.2461</v>
+        <v>3.1923</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1151,64 +1151,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4247</v>
+        <v>0.4619</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1191</v>
+        <v>0.9476</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6944</v>
+        <v>-0.4857</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.0301</v>
+        <v>-3.015</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4975</v>
+        <v>-1.4992</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5326</v>
+        <v>-1.5158</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3511</v>
+        <v>-0.4316</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0684</v>
+        <v>-1.1222</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7173</v>
+        <v>0.6906</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.679</v>
+        <v>-2.5834</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4292</v>
+        <v>-0.3769</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.2498</v>
+        <v>-2.2064</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6155</v>
+        <v>0.6407</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2373</v>
+        <v>0.1808</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3781</v>
+        <v>0.4599</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1234,64 +1234,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3937</v>
+        <v>0.4515</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5751</v>
+        <v>1.3944</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1815</v>
+        <v>-0.9429</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.836</v>
+        <v>-3.8246</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3029</v>
+        <v>-0.3522</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.5331</v>
+        <v>-3.4724</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0017</v>
+        <v>-0.1002</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0354</v>
+        <v>-0.1368</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0371</v>
+        <v>0.0366</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.8376</v>
+        <v>-3.7244</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2675</v>
+        <v>-0.2154</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.5702</v>
+        <v>-3.509</v>
       </c>
       <c r="P10" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2428</v>
+        <v>2.27</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6521</v>
+        <v>1.5943</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5907</v>
+        <v>0.6757</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1317,67 +1317,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1117</v>
+        <v>-0.113</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6038</v>
+        <v>0.4747</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7155</v>
+        <v>-0.5877</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2985</v>
+        <v>1.2497</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8508</v>
+        <v>1.79</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5523</v>
+        <v>-0.5403</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6456</v>
+        <v>1.5625</v>
       </c>
       <c r="K11" t="n">
-        <v>1.5715</v>
+        <v>1.4893</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0741</v>
+        <v>0.0732</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3471</v>
+        <v>-0.3128</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2793</v>
+        <v>0.3006</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6264</v>
+        <v>-0.6135</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6885</v>
+        <v>-0.7019</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R11" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5111</v>
+        <v>0.5376</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1056</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4055</v>
+        <v>0.4556</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.1126</v>
+        <v>-13.1003</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.4328</v>
+        <v>-10.666</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6798</v>
+        <v>-2.4343</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.261799999999999</v>
+        <v>-8.2059</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6038</v>
+        <v>0.6085</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.865600000000001</v>
+        <v>-8.814399999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.3533</v>
+        <v>-5.3886</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5215</v>
+        <v>0.4873</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.8748</v>
+        <v>-5.8759</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9085</v>
+        <v>-2.8173</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0824</v>
+        <v>0.1211</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.9908</v>
+        <v>-2.9385</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.1309</v>
+        <v>-4.2115</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.9669</v>
+        <v>-6.0833</v>
       </c>
       <c r="R12" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6834</v>
+        <v>1.7088</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1266</v>
+        <v>1.0693</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5568</v>
+        <v>0.6395</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.4033</v>
+        <v>-2.3917</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2393</v>
+        <v>-0.2634</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1079999999999988</v>
+        <v>-0.007899999999999352</v>
       </c>
       <c r="E13" t="n">
-        <v>10.8319</v>
+        <v>9.200499999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.94</v>
+        <v>-9.208600000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-11.8678</v>
+        <v>-11.9326</v>
       </c>
       <c r="H13" t="n">
-        <v>8.7455</v>
+        <v>8.413600000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-20.6133</v>
+        <v>-20.3464</v>
       </c>
       <c r="J13" t="n">
-        <v>7.247800000000001</v>
+        <v>6.445900000000002</v>
       </c>
       <c r="K13" t="n">
-        <v>10.3473</v>
+        <v>9.625299999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.0996</v>
+        <v>-3.1796</v>
       </c>
       <c r="M13" t="n">
-        <v>-19.1154</v>
+        <v>-18.3785</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.6018</v>
+        <v>-1.2118</v>
       </c>
       <c r="O13" t="n">
-        <v>-17.5136</v>
+        <v>-17.1669</v>
       </c>
       <c r="P13" t="n">
-        <v>1.147600000000001</v>
+        <v>1.169899999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.3274</v>
+        <v>-10.5288</v>
       </c>
       <c r="R13" t="n">
-        <v>11.475</v>
+        <v>11.6984</v>
       </c>
       <c r="S13" t="n">
-        <v>9.857800000000001</v>
+        <v>10.0832</v>
       </c>
       <c r="T13" t="n">
-        <v>6.3632</v>
+        <v>5.9586</v>
       </c>
       <c r="U13" t="n">
-        <v>3.4946</v>
+        <v>4.124499999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7544</v>
+        <v>0.6714999999999995</v>
       </c>
       <c r="W13" t="n">
-        <v>7.5482</v>
+        <v>7.3249</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.793800000000001</v>
+        <v>-6.6533</v>
       </c>
       <c r="Y13" t="inlineStr"/>
     </row>
@@ -1562,67 +1562,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4873</v>
+        <v>5.4</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0598</v>
+        <v>5.8329</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5725</v>
+        <v>-0.4329</v>
       </c>
       <c r="G14" t="n">
-        <v>5.1784</v>
+        <v>5.1427</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0318</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1466</v>
+        <v>5.079</v>
       </c>
       <c r="J14" t="n">
-        <v>6.178</v>
+        <v>6.0857</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6138</v>
+        <v>0.5977</v>
       </c>
       <c r="L14" t="n">
-        <v>5.5642</v>
+        <v>5.488</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9997</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.582</v>
+        <v>-0.534</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4176</v>
+        <v>-0.409</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.836</v>
+        <v>-1.8718</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R14" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1317</v>
+        <v>0.1351</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1382</v>
+        <v>-0.1756</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2699</v>
+        <v>0.3107</v>
       </c>
       <c r="V14" t="n">
-        <v>2.0132</v>
+        <v>1.9939</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3149</v>
+        <v>2.2625</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3017</v>
+        <v>-0.2686</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. ABROMAITIS</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1645,67 +1645,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7332</v>
+        <v>2.7323</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6795</v>
+        <v>1.0284</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0537</v>
+        <v>1.7039</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8836000000000001</v>
+        <v>2.102</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0566</v>
+        <v>-2.5855</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9401</v>
+        <v>4.6876</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9395</v>
+        <v>1.9117</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7715</v>
+        <v>-1.5265</v>
       </c>
       <c r="L15" t="n">
-        <v>1.711</v>
+        <v>3.4382</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.056</v>
+        <v>0.1903</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2851</v>
+        <v>-1.059</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2291</v>
+        <v>1.2494</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1475</v>
+        <v>1.8718</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.234</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1475</v>
+        <v>2.1057</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-1.1072</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4929</v>
+        <v>-0.6493</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0378</v>
+        <v>-0.4579</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2329</v>
+        <v>-0.1343</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2329</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>T. ABROMAITIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1728,67 +1728,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6863</v>
+        <v>2.6996</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1946</v>
+        <v>1.4902</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4917</v>
+        <v>1.2094</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0847</v>
+        <v>0.8815</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.6511</v>
+        <v>-1.037</v>
       </c>
       <c r="I16" t="n">
-        <v>4.7358</v>
+        <v>1.9185</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9848</v>
+        <v>0.8687</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.5046</v>
+        <v>-0.8126</v>
       </c>
       <c r="L16" t="n">
-        <v>3.4894</v>
+        <v>1.6813</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1</v>
+        <v>0.0128</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1464</v>
+        <v>-0.2244</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2464</v>
+        <v>0.2372</v>
       </c>
       <c r="P16" t="n">
-        <v>1.836</v>
+        <v>1.1699</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2295</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0655</v>
+        <v>1.1699</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0836</v>
+        <v>-0.5501</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5607</v>
+        <v>-0.5769</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5229</v>
+        <v>0.0267</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1509</v>
+        <v>1.1984</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1984</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1509</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3937</v>
+        <v>1.3771</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8716</v>
+        <v>1.6014</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4778</v>
+        <v>-0.2243</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3005</v>
+        <v>3.2725</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1989</v>
+        <v>1.2124</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1016</v>
+        <v>2.06</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0649</v>
+        <v>3.9372</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1924</v>
+        <v>2.1144</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8725</v>
+        <v>1.8228</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7644</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9936</v>
+        <v>-0.902</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2291</v>
+        <v>0.2372</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8345</v>
+        <v>-0.8607</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4394</v>
+        <v>-0.5282</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3951</v>
+        <v>-0.3326</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8427</v>
+        <v>-0.8007</v>
       </c>
       <c r="W17" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3838</v>
+        <v>-1.3327</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,67 +1894,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2003</v>
+        <v>1.2577</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6718</v>
+        <v>0.6257</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5285</v>
+        <v>0.632</v>
       </c>
       <c r="G18" t="n">
-        <v>1.316</v>
+        <v>1.3404</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0617</v>
+        <v>-0.0314</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3777</v>
+        <v>1.3719</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1191</v>
+        <v>1.1007</v>
       </c>
       <c r="K18" t="n">
-        <v>0.341</v>
+        <v>0.3321</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7781</v>
+        <v>0.7687</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1969</v>
+        <v>0.2397</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4027</v>
+        <v>-0.3635</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5996</v>
+        <v>0.6032</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0352</v>
+        <v>0.0516</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2178</v>
+        <v>-0.241</v>
       </c>
       <c r="U18" t="n">
-        <v>0.253</v>
+        <v>0.2926</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1977,22 +1977,22 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1617</v>
+        <v>0.1615</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1617</v>
+        <v>0.1615</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1617</v>
+        <v>0.1615</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1617</v>
+        <v>0.1615</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2004,13 +2004,13 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1617</v>
+        <v>0.1615</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1617</v>
+        <v>0.1615</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0181</v>
+        <v>-0.0629</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6188</v>
+        <v>-0.7696</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6007</v>
+        <v>0.7067</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2791</v>
+        <v>2.2579</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8985</v>
+        <v>1.8855</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3806</v>
+        <v>0.3724</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0439</v>
+        <v>1.9797</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1484</v>
+        <v>2.092</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1045</v>
+        <v>-0.1122</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2352</v>
+        <v>0.2782</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2498</v>
+        <v>-0.2064</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4851</v>
+        <v>0.4846</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R20" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7693</v>
+        <v>-0.7827</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3677</v>
+        <v>-0.4096</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4016</v>
+        <v>-0.3731</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,64 +2143,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2122</v>
+        <v>-0.2126</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0188</v>
+        <v>-0.1314</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2311</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2912</v>
+        <v>0.3012</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-0.6807</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9903</v>
+        <v>0.9819</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1821</v>
+        <v>1.1096</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5826</v>
+        <v>0.5264</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5995</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8909</v>
+        <v>-0.8084</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2817</v>
+        <v>-1.2071</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3908</v>
+        <v>0.3987</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.459</v>
+        <v>-0.4679</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="R21" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5855</v>
+        <v>-0.5779</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3273</v>
+        <v>-0.3692</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2582</v>
+        <v>-0.2087</v>
       </c>
       <c r="V21" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="W21" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2226,67 +2226,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2812</v>
+        <v>-0.2747</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7861</v>
+        <v>1.6093</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0673</v>
+        <v>-1.8841</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0231</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.761</v>
+        <v>-2.7049</v>
       </c>
       <c r="I22" t="n">
-        <v>1.738</v>
+        <v>1.7116</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1291</v>
+        <v>1.0496</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.959</v>
+        <v>-0.9952</v>
       </c>
       <c r="L22" t="n">
-        <v>2.0881</v>
+        <v>2.0449</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1522</v>
+        <v>-2.043</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.802</v>
+        <v>-1.7097</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3502</v>
+        <v>-0.3333</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="R22" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4877</v>
+        <v>-0.5154</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1956</v>
+        <v>-0.2705</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2921</v>
+        <v>-0.2449</v>
       </c>
       <c r="V22" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="W22" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2309,67 +2309,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6727</v>
+        <v>-1.7115</v>
       </c>
       <c r="E23" t="n">
-        <v>2.8868</v>
+        <v>2.6859</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.5595</v>
+        <v>-4.3974</v>
       </c>
       <c r="G23" t="n">
-        <v>1.8241</v>
+        <v>1.8024</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1799</v>
+        <v>-0.1629</v>
       </c>
       <c r="I23" t="n">
-        <v>2.004</v>
+        <v>1.9653</v>
       </c>
       <c r="J23" t="n">
-        <v>3.0383</v>
+        <v>2.9339</v>
       </c>
       <c r="K23" t="n">
-        <v>1.4252</v>
+        <v>1.3673</v>
       </c>
       <c r="L23" t="n">
-        <v>1.6132</v>
+        <v>1.5666</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2142</v>
+        <v>-1.1314</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6051</v>
+        <v>-1.5302</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3908</v>
+        <v>0.3987</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.918</v>
+        <v>-0.9359</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9558</v>
+        <v>-0.9819</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0861</v>
+        <v>-0.1423</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8697</v>
+        <v>-0.8396</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.623</v>
+        <v>-1.5962</v>
       </c>
       <c r="W23" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.705</v>
+        <v>-2.6603</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,58 +2392,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4907</v>
+        <v>-3.4867</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7728</v>
+        <v>-3.8794</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2821</v>
+        <v>0.3927</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.9326</v>
+        <v>-2.9045</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.202</v>
+        <v>-3.1671</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2694</v>
+        <v>0.2626</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.0946</v>
+        <v>-2.1231</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.62</v>
+        <v>-2.6331</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5254</v>
+        <v>0.51</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.838</v>
+        <v>-0.7814</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.582</v>
+        <v>-0.534</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2559</v>
+        <v>-0.2474</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R24" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7876</v>
+        <v>-0.8162</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.5865</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2569</v>
+        <v>-0.2297</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.098</v>
+        <v>-4</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8375</v>
+        <v>-0.8848</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2606</v>
+        <v>-3.1151</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.4959</v>
+        <v>-1.4317</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.2635</v>
+        <v>-1.2057</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2324</v>
+        <v>-0.226</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4697</v>
+        <v>-0.4753</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1535</v>
+        <v>0.1494</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6232</v>
+        <v>-0.6247</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.0261</v>
+        <v>-0.9564</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.4169</v>
+        <v>-1.3552</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3908</v>
+        <v>0.3987</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2086</v>
+        <v>-0.2061</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1382</v>
+        <v>-0.1756</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0704</v>
+        <v>-0.0305</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2558,67 +2558,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3.889600000000001</v>
+        <v>3.879800000000002</v>
       </c>
       <c r="E26" t="n">
-        <v>10.9399</v>
+        <v>9.208599999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.0504</v>
+        <v>-5.3288</v>
       </c>
       <c r="G26" t="n">
-        <v>11.8677</v>
+        <v>11.9325</v>
       </c>
       <c r="H26" t="n">
-        <v>-8.745699999999999</v>
+        <v>-8.413600000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>20.61340000000001</v>
+        <v>20.3463</v>
       </c>
       <c r="J26" t="n">
-        <v>19.1154</v>
+        <v>18.3784</v>
       </c>
       <c r="K26" t="n">
-        <v>1.6018</v>
+        <v>1.2119</v>
       </c>
       <c r="L26" t="n">
-        <v>17.5137</v>
+        <v>17.1668</v>
       </c>
       <c r="M26" t="n">
-        <v>-7.2477</v>
+        <v>-6.4459</v>
       </c>
       <c r="N26" t="n">
-        <v>-10.3473</v>
+        <v>-9.625500000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>3.0997</v>
+        <v>3.1795</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.1475</v>
+        <v>-1.1698</v>
       </c>
       <c r="Q26" t="n">
-        <v>-11.475</v>
+        <v>-11.6987</v>
       </c>
       <c r="R26" t="n">
-        <v>10.3275</v>
+        <v>10.5287</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.0764</v>
+        <v>-6.2115</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.4946</v>
+        <v>-4.1247</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.5818</v>
+        <v>-2.087</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.7543</v>
+        <v>-0.6715</v>
       </c>
       <c r="W26" t="n">
-        <v>6.793800000000001</v>
+        <v>6.6533</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.5482</v>
+        <v>-7.3248</v>
       </c>
       <c r="Y26" t="inlineStr"/>
     </row>
